--- a/XLS/S1/S1.xlsx
+++ b/XLS/S1/S1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohammed Al-Emara\Documents\GitHub\Statistical-notebook\XLS\S1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCC85F5-C41A-4C1E-87E8-034ADAE16DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B1E24C-D819-494F-8BD2-29596999C1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13877,14 +13877,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17821,7 +17821,7 @@
       <c r="O10" s="2" t="s">
         <v>4440</v>
       </c>
-      <c r="Q10" s="64" t="s">
+      <c r="Q10" s="62" t="s">
         <v>4455</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -58485,8 +58485,8 @@
       </c>
     </row>
     <row r="2116" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2116" s="62"/>
-      <c r="B2116" s="63"/>
+      <c r="A2116" s="63"/>
+      <c r="B2116" s="64"/>
       <c r="C2116" s="57"/>
       <c r="D2116" s="57"/>
       <c r="E2116" s="57"/>
@@ -60023,8 +60023,8 @@
       </c>
     </row>
     <row r="2200" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2200" s="62"/>
-      <c r="B2200" s="63"/>
+      <c r="A2200" s="63"/>
+      <c r="B2200" s="64"/>
       <c r="C2200" s="57"/>
       <c r="D2200" s="57"/>
       <c r="E2200" s="57"/>
@@ -61562,8 +61562,8 @@
       </c>
     </row>
     <row r="2286" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2286" s="62"/>
-      <c r="B2286" s="63"/>
+      <c r="A2286" s="63"/>
+      <c r="B2286" s="64"/>
       <c r="C2286" s="57"/>
       <c r="D2286" s="57"/>
       <c r="E2286" s="57"/>
@@ -62484,8 +62484,8 @@
       </c>
     </row>
     <row r="2339" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2339" s="62"/>
-      <c r="B2339" s="63"/>
+      <c r="A2339" s="63"/>
+      <c r="B2339" s="64"/>
       <c r="C2339" s="57"/>
       <c r="D2339" s="57"/>
       <c r="E2339" s="57"/>
@@ -63407,8 +63407,8 @@
       </c>
     </row>
     <row r="2392" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2392" s="62"/>
-      <c r="B2392" s="63"/>
+      <c r="A2392" s="63"/>
+      <c r="B2392" s="64"/>
       <c r="C2392" s="57"/>
       <c r="D2392" s="57"/>
       <c r="E2392" s="57"/>
@@ -64447,8 +64447,8 @@
       </c>
     </row>
     <row r="2451" spans="1:18" s="55" customFormat="1" ht="13.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2451" s="62"/>
-      <c r="B2451" s="63"/>
+      <c r="A2451" s="63"/>
+      <c r="B2451" s="64"/>
       <c r="C2451" s="57"/>
       <c r="D2451" s="57"/>
       <c r="E2451" s="57"/>
